--- a/file/Power_Apps_Pro_and_Premium_Developer_Tools_Win32_VPATJ12360.xlsx
+++ b/file/Power_Apps_Pro_and_Premium_Developer_Tools_Win32_VPATJ12360.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDB46742-864F-4889-A53D-94F07748A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB7F0BE3-8F93-4BA8-A43F-FDFD7C730710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{8C9595EC-DCE7-44A9-8824-5BE53BDBEE07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{9FA20FED-67EA-422B-9ECE-3F6C401B3F3A}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -60,12 +60,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="227">
   <si>
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年10月1日</t>
+    <t>作成日：2025年3月28日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -139,6 +139,20 @@
   </si>
   <si>
     <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>部分的に対応している</t>
+    <rPh sb="0" eb="3">
+      <t>ブブンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Plugin Registration Tool: コントラストモードの水中、夕暮れ、夜空テーマを適用した後、ログインダイアログのテキストが表示されません。</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2017,8 +2031,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED1FDF62-58A3-4CEB-B865-40C9C82C73E9}">
-  <sheetPr codeName="Sheet297">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1BBDBF-A65B-4170-9FF9-3EE57612AFA8}">
+  <sheetPr codeName="Sheet333">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2296,10 +2310,10 @@
       <c r="B20" s="33"/>
       <c r="C20" s="34"/>
       <c r="D20" s="46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
@@ -2308,7 +2322,7 @@
     </row>
     <row r="21" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="39" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
@@ -2321,15 +2335,15 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B22" s="33"/>
       <c r="C22" s="34"/>
       <c r="D22" s="42" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="42"/>
@@ -2338,7 +2352,7 @@
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
@@ -2351,7 +2365,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
@@ -2368,7 +2382,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2381,7 +2395,7 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
@@ -2398,7 +2412,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2411,15 +2425,15 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
@@ -2428,7 +2442,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -2441,7 +2455,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -2458,7 +2472,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -2471,7 +2485,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -2484,7 +2498,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -2497,15 +2511,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -2514,7 +2528,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -2555,15 +2569,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -2572,7 +2586,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -2596,7 +2610,7 @@
     </row>
     <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2626,15 +2640,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -2643,7 +2657,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -2667,10 +2681,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -2693,7 +2707,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -2833,7 +2847,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{2AF23C4E-8162-42D6-8B96-B57CDA73CFF8}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{1269A647-B426-48D3-8BEF-0A89E26E5BED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2841,7 +2855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8C5380-A479-4AF8-B427-72EEE8E0D438}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07B56C7-40BB-4731-B698-9F5261866A49}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2854,16 +2868,16 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="60" t="s">
         <v>18</v>
@@ -2872,25 +2886,25 @@
         <v>22</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2898,36 +2912,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2935,10 +2949,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -2956,14 +2970,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -2979,15 +2993,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3002,15 +3016,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3025,17 +3039,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3048,10 +3062,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3059,7 +3073,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3071,10 +3085,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3083,7 +3097,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3094,10 +3108,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3107,10 +3121,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3119,10 +3133,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3132,10 +3146,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3144,10 +3158,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3165,17 +3179,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3190,10 +3204,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3211,10 +3225,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3229,17 +3243,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3252,17 +3266,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3275,20 +3289,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3300,20 +3314,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3325,17 +3339,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3351,10 +3365,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3362,7 +3376,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3371,23 +3385,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3396,23 +3410,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3424,15 +3438,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3447,15 +3461,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -3470,27 +3484,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -3499,10 +3513,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -3520,29 +3534,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -3551,10 +3565,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -3572,17 +3586,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -3597,10 +3611,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -3618,30 +3632,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3649,10 +3663,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -3670,31 +3684,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -3703,10 +3717,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -3724,15 +3738,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -3747,14 +3761,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -3770,10 +3784,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -3783,10 +3797,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -3795,27 +3809,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -3824,10 +3838,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -3837,10 +3851,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -3849,14 +3863,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -3872,10 +3886,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -3885,10 +3899,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -3897,10 +3911,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -3910,10 +3924,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -3922,10 +3936,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -3943,10 +3957,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -3964,10 +3978,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -3985,14 +3999,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4008,10 +4022,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4029,15 +4043,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4052,10 +4066,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4073,20 +4087,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4098,10 +4112,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4119,29 +4133,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4150,10 +4164,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4171,10 +4185,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4182,7 +4196,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4194,10 +4208,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4205,7 +4219,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4217,10 +4231,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4228,7 +4242,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4240,10 +4254,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4261,24 +4275,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4290,17 +4304,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4313,20 +4327,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4338,10 +4352,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4359,14 +4373,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4382,10 +4396,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4403,22 +4417,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4430,10 +4444,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4451,31 +4465,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -4484,10 +4498,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -4505,29 +4519,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -4536,14 +4550,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -4551,10 +4565,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -4563,43 +4577,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -4609,22 +4623,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -4634,22 +4648,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -4659,32 +4673,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -4693,23 +4707,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -4718,26 +4732,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -4745,23 +4759,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -4773,31 +4787,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -4806,10 +4820,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -4827,15 +4841,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -4850,14 +4864,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -4865,10 +4879,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -4877,22 +4891,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -4904,24 +4918,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -4933,10 +4947,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -4954,24 +4968,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -4980,25 +4994,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5007,20 +5021,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5035,24 +5049,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5064,24 +5078,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
